--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486400_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486400_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2269</v>
+        <v>1.8222</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6214</v>
+        <v>3.0626</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3944</v>
+        <v>-1.2403</v>
       </c>
       <c r="G2" t="n">
         <v>2.2611</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5738</v>
+        <v>0.1691</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5312</v>
+        <v>-0.0276</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0427</v>
+        <v>0.1968</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3904</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. CRUZ UCEDA</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0033</v>
+        <v>1.1059</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3715</v>
+        <v>1.3978</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3682</v>
+        <v>-0.2919</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3239</v>
+        <v>1.1777</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.0151</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>5.339</v>
+        <v>1.9444</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1905</v>
+        <v>2.7605</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.7398</v>
+        <v>0.7117</v>
       </c>
       <c r="L3" t="n">
-        <v>5.9303</v>
+        <v>2.0488</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.8666</v>
+        <v>-1.5827</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.2753</v>
+        <v>-1.4783</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5913</v>
+        <v>-0.1044</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3926</v>
+        <v>-1.305</v>
       </c>
       <c r="R3" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0274</v>
+        <v>-0.2034</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5564</v>
+        <v>-0.0577</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5838</v>
+        <v>-0.1457</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7395</v>
+        <v>0.3491</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3904</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4821</v>
+        <v>0.8828</v>
       </c>
       <c r="E4" t="n">
         <v>2.0458</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5638</v>
+        <v>-1.1631</v>
       </c>
       <c r="G4" t="n">
         <v>1.7852</v>
@@ -766,13 +766,13 @@
         <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4983</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>-0.2139</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2844</v>
+        <v>0.1163</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3698</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>I. CRUZ UCEDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.393</v>
+        <v>0.4986</v>
       </c>
       <c r="E5" t="n">
-        <v>0.839</v>
+        <v>1.4832</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.446</v>
+        <v>-0.9846</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1777</v>
+        <v>0.3239</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-5.0151</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9444</v>
+        <v>5.339</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7605</v>
+        <v>3.1905</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7117</v>
+        <v>-2.7398</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0488</v>
+        <v>5.9303</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5827</v>
+        <v>-2.8666</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4783</v>
+        <v>-2.2753</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1044</v>
+        <v>-0.5913</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.305</v>
+        <v>-2.3926</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9163</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6165</v>
+        <v>-0.4446</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2998</v>
+        <v>0.9673</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3491</v>
+        <v>0.7395</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3491</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0939</v>
+        <v>0.1478</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1593</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0654</v>
+        <v>0.212</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0586</v>
@@ -922,13 +922,13 @@
         <v>0.2175</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1525</v>
+        <v>0.2064</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2656</v>
+        <v>0.0421</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1131</v>
+        <v>0.1643</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3719</v>
+        <v>-0.2023</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6324</v>
+        <v>1.0794</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0043</v>
+        <v>-1.2817</v>
       </c>
       <c r="G7" t="n">
         <v>0.2136</v>
@@ -1000,13 +1000,13 @@
         <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.108</v>
+        <v>0.0616</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.548</v>
+        <v>-0.1009</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4399</v>
+        <v>0.1625</v>
       </c>
       <c r="V7" t="n">
         <v>-1.13</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0623</v>
+        <v>-1.3667</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7097</v>
+        <v>0.3745</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.772</v>
+        <v>-1.7412</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6821</v>
@@ -1078,13 +1078,13 @@
         <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4676</v>
+        <v>0.1631</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4026</v>
+        <v>0.0673</v>
       </c>
       <c r="U8" t="n">
-        <v>0.065</v>
+        <v>0.0958</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1952</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3998</v>
+        <v>-2.0184</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2944</v>
+        <v>-0.4062</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1054</v>
+        <v>-1.6122</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4646</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4127</v>
+        <v>-0.0312</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4879</v>
+        <v>-0.5996</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0752</v>
+        <v>0.5684</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. POIRIER</t>
+          <t>S. RODRIGUEZ FEBLES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6437</v>
+        <v>-2.7185</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.971</v>
+        <v>-1.2421</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3273</v>
+        <v>-1.4763</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4637</v>
+        <v>0.0226</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.125</v>
+        <v>-2.4756</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3387</v>
+        <v>2.4982</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.575</v>
+        <v>2.4819</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2761</v>
+        <v>0.2618</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2989</v>
+        <v>2.2201</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8887</v>
+        <v>-2.4593</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8488</v>
+        <v>-2.7374</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0399</v>
+        <v>0.2781</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7401</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R10" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>1.56</v>
+        <v>-0.3485</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3509</v>
+        <v>-0.4614</v>
       </c>
       <c r="U10" t="n">
-        <v>1.9109</v>
+        <v>0.113</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ FEBLES</t>
+          <t>D. POIRIER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1886</v>
+        <v>-3.6185</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4657</v>
+        <v>-3.0827</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7229</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0226</v>
+        <v>-2.4637</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.4756</v>
+        <v>-1.125</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4982</v>
+        <v>-1.3387</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4819</v>
+        <v>-1.575</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2618</v>
+        <v>-0.2761</v>
       </c>
       <c r="L11" t="n">
-        <v>2.2201</v>
+        <v>-1.2989</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4593</v>
+        <v>-0.8887</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.7374</v>
+        <v>-0.8488</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2781</v>
+        <v>-0.0399</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.3926</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8186</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.4626</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1336</v>
+        <v>1.0479</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="12">
@@ -1348,13 +1348,13 @@
         <v>-5.4671</v>
       </c>
       <c r="E12" t="n">
-        <v>4.647999999999998</v>
+        <v>4.648099999999999</v>
       </c>
       <c r="F12" t="n">
         <v>-10.1151</v>
       </c>
       <c r="G12" t="n">
-        <v>2.115100000000001</v>
+        <v>2.1151</v>
       </c>
       <c r="H12" t="n">
         <v>-12.4398</v>
@@ -1378,7 +1378,7 @@
         <v>-15.6958</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0238000000000001</v>
+        <v>0.02380000000000009</v>
       </c>
       <c r="P12" t="n">
         <v>-7.6127</v>
@@ -1393,7 +1393,7 @@
         <v>1.0274</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.2592</v>
+        <v>-2.2589</v>
       </c>
       <c r="U12" t="n">
         <v>3.2866</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0211</v>
+        <v>6.0326</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1535</v>
+        <v>6.0417</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1324</v>
+        <v>-0.0091</v>
       </c>
       <c r="G13" t="n">
         <v>4.7609</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2603</v>
+        <v>-0.2488</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6249</v>
+        <v>-0.7366</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3646</v>
+        <v>0.4879</v>
       </c>
       <c r="V13" t="n">
         <v>1.5204</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4193</v>
+        <v>3.1814</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9687</v>
+        <v>5.8434</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4505</v>
+        <v>-2.662</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6364</v>
+        <v>0.081</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0349</v>
+        <v>3.2939</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3984</v>
+        <v>-3.2129</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1897</v>
+        <v>3.8136</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6342</v>
+        <v>3.9268</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5554</v>
+        <v>-0.1131</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5532</v>
+        <v>-3.7327</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5994</v>
+        <v>-0.6328</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9539</v>
+        <v>-3.0998</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6953</v>
+        <v>-0.1824</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1334</v>
+        <v>-0.4254</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8287</v>
+        <v>0.243</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3124</v>
+        <v>2.9877</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0669</v>
+        <v>1.9687</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.7545</v>
+        <v>1.019</v>
       </c>
       <c r="G15" t="n">
-        <v>0.081</v>
+        <v>1.6364</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2939</v>
+        <v>2.0349</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.2129</v>
+        <v>-0.3984</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8136</v>
+        <v>3.1897</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9268</v>
+        <v>2.6342</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1131</v>
+        <v>0.5554</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.7327</v>
+        <v>-1.5532</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6328</v>
+        <v>-0.5994</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.0998</v>
+        <v>-0.9539</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0513</v>
+        <v>0.2638</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2019</v>
+        <v>-0.1334</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1506</v>
+        <v>0.3972</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9013</v>
+        <v>1.013</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1612</v>
+        <v>0.273</v>
       </c>
       <c r="F16" t="n">
         <v>0.7401</v>
@@ -1702,10 +1702,10 @@
         <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.262</v>
+        <v>-0.1502</v>
       </c>
       <c r="U16" t="n">
         <v>0.1935</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5209</v>
+        <v>0.3089</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8915</v>
+        <v>-1.2268</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4124</v>
+        <v>1.5357</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6234</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0308</v>
+        <v>-0.2427</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1406</v>
+        <v>-0.1947</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1714</v>
+        <v>-0.0481</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5649999999999999</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6519</v>
+        <v>-0.1741</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1817</v>
+        <v>-0.7347</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5298</v>
+        <v>0.5606</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9705</v>
@@ -1858,13 +1858,13 @@
         <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5515</v>
+        <v>-0.0736</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6609</v>
+        <v>-0.2139</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1095</v>
+        <v>0.1403</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. IDEHEN IDEHEN</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7017</v>
+        <v>-0.7674</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6084000000000001</v>
+        <v>1.2324</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3101</v>
+        <v>-1.9998</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.012</v>
+        <v>1.3636</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6781</v>
+        <v>1.0735</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6901</v>
+        <v>0.29</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8447</v>
+        <v>4.5672</v>
       </c>
       <c r="K19" t="n">
-        <v>0.73</v>
+        <v>1.7734</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1147</v>
+        <v>2.7938</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8567</v>
+        <v>-3.2036</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0519</v>
+        <v>-0.6998</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-2.5038</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5273</v>
+        <v>-0.3464</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.822</v>
+        <v>-0.4626</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3492</v>
+        <v>0.1163</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8695</v>
+        <v>0.3904</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5857</v>
+        <v>0.3904</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>E. IDEHEN IDEHEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5034</v>
+        <v>-1.268</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8971</v>
+        <v>0.7202</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4005</v>
+        <v>-1.9882</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3636</v>
+        <v>-0.012</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0735</v>
+        <v>0.6781</v>
       </c>
       <c r="I20" t="n">
-        <v>0.29</v>
+        <v>-0.6901</v>
       </c>
       <c r="J20" t="n">
-        <v>4.5672</v>
+        <v>0.8447</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7734</v>
+        <v>0.73</v>
       </c>
       <c r="L20" t="n">
-        <v>2.7938</v>
+        <v>0.1147</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.2036</v>
+        <v>-0.8567</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6998</v>
+        <v>-0.0519</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.5038</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.1751</v>
+        <v>0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0824</v>
+        <v>-0.0391</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2844</v>
+        <v>0.6711</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3904</v>
+        <v>-1.8695</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3904</v>
+        <v>0.5857</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5373</v>
+        <v>-2.2637</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4783</v>
+        <v>-1.143</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.059</v>
+        <v>-1.1207</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3287</v>
@@ -2092,13 +2092,13 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1216</v>
+        <v>0.152</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.125</v>
+        <v>0.2103</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0034</v>
+        <v>-0.0583</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7395</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3134</v>
+        <v>-3.5833</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1893</v>
+        <v>-2.8598</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1242</v>
+        <v>-0.7235</v>
       </c>
       <c r="G22" t="n">
         <v>-5.6445</v>
@@ -2170,13 +2170,13 @@
         <v>2.6101</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0837</v>
+        <v>-0.3536</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2007</v>
+        <v>-0.4698</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2844</v>
+        <v>0.1163</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1952</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.4673</v>
+        <v>5.4671</v>
       </c>
       <c r="E23" t="n">
-        <v>10.115</v>
+        <v>10.1151</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.647900000000001</v>
+        <v>-4.6479</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1149</v>
+        <v>-2.114899999999999</v>
       </c>
       <c r="H23" t="n">
         <v>12.4396</v>
@@ -2251,13 +2251,13 @@
         <v>-1.0275</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.2867</v>
+        <v>-3.2865</v>
       </c>
       <c r="U23" t="n">
-        <v>2.259300000000001</v>
+        <v>2.2592</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9967999999999997</v>
+        <v>0.9968000000000001</v>
       </c>
       <c r="W23" t="n">
         <v>5.3422</v>
